--- a/cancellazioni_mdr.xlsx
+++ b/cancellazioni_mdr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaia/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00168656-55D4-5448-8980-6C677E9F2FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBBA319-E2B0-4242-8FC2-4790CDA182AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9200" yWindow="1760" windowWidth="27640" windowHeight="16680" xr2:uid="{BF3DEF59-FA33-A440-BFA2-891740C34FEB}"/>
+    <workbookView xWindow="6560" yWindow="1760" windowWidth="27640" windowHeight="16680" xr2:uid="{BF3DEF59-FA33-A440-BFA2-891740C34FEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C1">
         <v>2014</v>
